--- a/DATA/ENGINEER SCHEDULES/Barrett Woodyard & Associates.xlsx
+++ b/DATA/ENGINEER SCHEDULES/Barrett Woodyard & Associates.xlsx
@@ -1,27 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HHpro\DATA\ENGINEER SCHEDULES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProgramData\HHpro\DATA\ENGINEER SCHEDULES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41244E6F-DDC0-46FA-B8DC-3B7F3B883AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D3AD91-EC54-4CC8-A6F3-9C4A7060B1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MULTI POSITION SPLIT" sheetId="1" r:id="rId1"/>
-    <sheet name="RTU" sheetId="2" r:id="rId2"/>
+    <sheet name="RTU" sheetId="3" r:id="rId1"/>
+    <sheet name="MULTI POSITION SPLIT" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="MSch_ERV">#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RTU!$B$1:$X$14</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="109">
   <si>
     <t>SPLIT SYSTEM SCHEDULE</t>
   </si>
@@ -242,12 +246,6 @@
     <t>MOCP</t>
   </si>
   <si>
-    <t>INPUT</t>
-  </si>
-  <si>
-    <t>OUTPUT</t>
-  </si>
-  <si>
     <t>RTU-1</t>
   </si>
   <si>
@@ -260,206 +258,170 @@
     <t>RTU-2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>I.D. TAG</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MINIMUM TOTAL CAP. (MBH)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MINIMUM SENSIBLE CAP. (MBH)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AMBIENT TEMP (°F)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>COIL EAT</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AIRFLOW (CFM)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MAX H.P.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VOLTS/ PHASE</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BASIS OF DESIGN</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>APPROX. UNIT WEIGHT (LBS)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>°F db</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>°F wb</t>
-    </r>
-  </si>
-  <si>
-    <t>EXT. S.P.
-(IN. W.C.)</t>
-  </si>
-  <si>
     <t>HEATING</t>
   </si>
   <si>
-    <t>① THIS IS THE STATIC PRESSURE EXTERNAL TO THE UNIT. IT DOES NOT INCLUDE COIL, CASING, FILTER, OR HEATER LOSSES</t>
-  </si>
-  <si>
-    <t>② PROVIDE UNIT COMPLETE FACTORY DISCONNECT W/ LOCKOUT PROTECTION CAPABILITY.</t>
-  </si>
-  <si>
-    <t>③ CAPACITY IN MBH.</t>
-  </si>
-  <si>
-    <t>⑤ PROVIDE SMOKE DETECTOR IN UNIT SUPPLY AND RETURN. INSTALLATION SHALL BE IN ACCORDANCE WITH NFPA 72E. COORD. W/ DIVISION 16.</t>
-  </si>
-  <si>
-    <t>⑥ POWERED WEATHERPROOF GFI DEDICATED CONVENIENCE OUTLET TO BE PROVIDED, COORDINATE WITH ELECTRICAL.</t>
-  </si>
-  <si>
-    <t>④ SUPPLY FAN SHALL BE CAPABLE OF SUPPLYING AIRFLOW AT CFM &amp; E.S.P. (IN. W.C.) AS INDICATED ON SCHEDULED ABOVE</t>
-  </si>
-  <si>
-    <t>⑦ PROVIDE UNIT WITH COMPARATIVE ENTHALPY ECONOMIZER</t>
-  </si>
-  <si>
-    <t>⑧ PROVIDE WITH HAIL GUARD</t>
-  </si>
-  <si>
-    <t>⑨ PROVIDE WITH 2 MULTI-STAGE COMPRESSORS.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PACKAGED  ROOF TOP UNITS</t>
-    </r>
-  </si>
-  <si>
-    <t>DAIKIN DSG0363DL</t>
-  </si>
-  <si>
-    <t>DAIKIN DSG0484DH</t>
-  </si>
-  <si>
     <t>460/3</t>
   </si>
   <si>
-    <t>EFFICIENCY (AT AHRI)</t>
-  </si>
-  <si>
-    <t>14.0 SEER2/12.0 EER2</t>
-  </si>
-  <si>
-    <t>13.7 SEER2/11.8 EER2</t>
-  </si>
-  <si>
-    <t>① ② ③ ④ ⑤ ⑥ ⑦ ⑧ ⑨</t>
-  </si>
-  <si>
-    <t>OUTSIDE AIR
-(CFM)</t>
+    <t>PACKAGED ROOFTOP UNIT SCHEDULE</t>
+  </si>
+  <si>
+    <t>I.D.</t>
+  </si>
+  <si>
+    <t>SUPPLY</t>
+  </si>
+  <si>
+    <t>EXT. SP</t>
+  </si>
+  <si>
+    <t>MOTOR</t>
+  </si>
+  <si>
+    <t>BOD TOTAL</t>
+  </si>
+  <si>
+    <t>BOD SENSIBLE</t>
+  </si>
+  <si>
+    <t>AMBIENT</t>
+  </si>
+  <si>
+    <t>COIL EAT</t>
+  </si>
+  <si>
+    <t>EER</t>
+  </si>
+  <si>
+    <t>SEER2/</t>
+  </si>
+  <si>
+    <t>COP 
+(47°F)/(17°F)</t>
+  </si>
+  <si>
+    <t>VOLTS/</t>
+  </si>
+  <si>
+    <t>BASIS OF DESIGN</t>
+  </si>
+  <si>
+    <t>APPROX.</t>
+  </si>
+  <si>
+    <t>TAG</t>
+  </si>
+  <si>
+    <t>AIRFLOW (CFM)</t>
+  </si>
+  <si>
+    <t>(IN. WC) (1)</t>
+  </si>
+  <si>
+    <t>CAPACITY (MBH)</t>
+  </si>
+  <si>
+    <t>TEMP (°F)</t>
+  </si>
+  <si>
+    <t>°F db</t>
+  </si>
+  <si>
+    <t>°F wb</t>
+  </si>
+  <si>
+    <t>GAS INPUT</t>
+  </si>
+  <si>
+    <t>HEAT PUMP BTU/h (47°F, 70°F Indoor DB)</t>
+  </si>
+  <si>
+    <t>HEAT PUMP BTU/h (17°F, 70°F Indoor DB)</t>
+  </si>
+  <si>
+    <t>IEER</t>
+  </si>
+  <si>
+    <t>PHASE</t>
+  </si>
+  <si>
+    <t>WEIGHT (LBS)</t>
+  </si>
+  <si>
+    <t>DAIKIN DSG0483DL</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>DAIKIN DSG0603DL</t>
+  </si>
+  <si>
+    <t>RTU-3</t>
+  </si>
+  <si>
+    <t>HEAT PUMP</t>
+  </si>
+  <si>
+    <t>3.5/2.4</t>
+  </si>
+  <si>
+    <t>DAIKIN DHH0724</t>
+  </si>
+  <si>
+    <t>RTU-4</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>3.3/2.05</t>
+  </si>
+  <si>
+    <t>DAIKIN DSH2403</t>
+  </si>
+  <si>
+    <t>(1)  THIS IS THE SP EXTERNAL TO THE ENTIRE UNIT ASSEMBLY (WET COIL, CASING, CLEAN FILTERS, AND FURNACE LOSSES ARE NOT INCLUDED IN THIS EXTERNAL SP).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)  HEAT PUMP CAPACITY RATED AT 17°F. </t>
+  </si>
+  <si>
+    <t>(3)  PROVIDE WITH POWERED GFI OUTLET. COORD. WITH DIV. 26.</t>
+  </si>
+  <si>
+    <t>(4)  PROVIDE WITH INTEGRAL DISCONNECT. COORD. WITH DIV. 26.</t>
+  </si>
+  <si>
+    <t>(5)  PROVIDE SMOKE DETECTORS RETURN DUCTWORK FOR AUTOMATIC SHUTDOWN IN COMPLIANCE WITH NFPA 72.  DETECTORS SHALL BE SUPPLIED BY DIV. 26 AND INSTALLED BY DIV. 23.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6)  PROVIDE WITH 7-DAY PROGRAMMABLE TSTAT OR INTERLOCK TO BAS. </t>
+  </si>
+  <si>
+    <t>(7)  PROVIDE UNIT WITH DIFFERENTIAL-ENTHALPY ECONOMIZER AND BAROMETRIC RELIEF.</t>
+  </si>
+  <si>
+    <t>(8)  PROVIDE UNIT WITH DIFFERENTIAL-ENTHALPY ECONOMIZER AND POWERED EXHAUST</t>
+  </si>
+  <si>
+    <t>(9)  PROVIDE WITH HOT GAS REHEAT AND SPACE-MOUNTED TEMPERATURE/HUMIDITY SENSOR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10) PROVIDE UNIT WITH PLENUM RETURN CURB. </t>
+  </si>
+  <si>
+    <t>(11) PROVIDE WITH ECM SUPPLY FAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(12) PROVIDE WITH MODULATING OUTSIDE AIR DAMPER, INTERLOCKED TO SPACE-MOUNTED CO2 SENSOR FOR DEMAND CONTROL VENTILATION SEQUENCE. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13) FOR ALL HEALTHCARE APPLICATIONS OUTSIDE AIR INTAKE SHALL BE A MINIMUM OF 36" ABOVE THE ADJACENT ROOF. PROVIDE WITH EXTENDED HEIGHT CURB AS REQUIRED. </t>
+  </si>
+  <si>
+    <t>GAS OUTPUT</t>
   </si>
 </sst>
 </file>
@@ -468,9 +430,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -503,11 +465,18 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -518,7 +487,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -528,29 +497,29 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -558,81 +527,261 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -641,6 +790,62 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -656,7 +861,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -666,25 +873,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -693,35 +891,34 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
@@ -731,7 +928,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -739,12 +936,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -753,39 +950,29 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -801,250 +988,224 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{22D40CD6-3468-48AA-9F7C-A9CA90D35AEC}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{1641768B-D2A1-49F9-926D-6E016A8C89FC}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1345,6 +1506,580 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C933EDCF-C85F-43FD-83FB-632E043433FC}">
+  <dimension ref="B1:X21"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.1640625" style="21" customWidth="1"/>
+    <col min="2" max="2" width="11" style="21" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="14" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="21" customWidth="1"/>
+    <col min="6" max="7" width="18.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="44" style="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5" style="21" customWidth="1"/>
+    <col min="18" max="18" width="14.5" style="21" customWidth="1"/>
+    <col min="19" max="19" width="8.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="8.5" style="21" customWidth="1"/>
+    <col min="22" max="22" width="22.1640625" style="21" customWidth="1"/>
+    <col min="23" max="23" width="16" style="21" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="25.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.1640625" style="21" customWidth="1"/>
+    <col min="26" max="16384" width="9.33203125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:24" ht="24" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
+      <c r="S1" s="58"/>
+      <c r="T1" s="58"/>
+      <c r="U1" s="58"/>
+      <c r="V1" s="58"/>
+      <c r="W1" s="58"/>
+      <c r="X1" s="59"/>
+    </row>
+    <row r="2" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B2" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="61"/>
+      <c r="K2" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="R2" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="S2" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="T2" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="U2" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="V2" s="66" t="s">
+        <v>69</v>
+      </c>
+      <c r="W2" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="X2" s="68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:24" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="N3" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="R3" s="64"/>
+      <c r="S3" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X3" s="69"/>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B4" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="36">
+        <v>1655</v>
+      </c>
+      <c r="D4" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="37">
+        <v>1</v>
+      </c>
+      <c r="F4" s="36">
+        <v>46.201999999999998</v>
+      </c>
+      <c r="G4" s="36">
+        <v>36.218000000000004</v>
+      </c>
+      <c r="H4" s="36">
+        <v>95</v>
+      </c>
+      <c r="I4" s="36">
+        <v>80</v>
+      </c>
+      <c r="J4" s="36">
+        <v>67</v>
+      </c>
+      <c r="K4" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" s="37">
+        <v>70</v>
+      </c>
+      <c r="M4" s="37">
+        <v>56</v>
+      </c>
+      <c r="N4" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="37">
+        <v>11.8</v>
+      </c>
+      <c r="Q4" s="37">
+        <v>13.7</v>
+      </c>
+      <c r="R4" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="T4" s="36">
+        <v>24.1</v>
+      </c>
+      <c r="U4" s="36">
+        <v>35</v>
+      </c>
+      <c r="V4" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="W4" s="37">
+        <v>548</v>
+      </c>
+      <c r="X4" s="38"/>
+    </row>
+    <row r="5" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B5" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="40">
+        <v>2090</v>
+      </c>
+      <c r="D5" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="40">
+        <v>58.473999999999997</v>
+      </c>
+      <c r="G5" s="40">
+        <v>45.127000000000002</v>
+      </c>
+      <c r="H5" s="40">
+        <v>95</v>
+      </c>
+      <c r="I5" s="40">
+        <v>80</v>
+      </c>
+      <c r="J5" s="40">
+        <v>67</v>
+      </c>
+      <c r="K5" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" s="41">
+        <v>90</v>
+      </c>
+      <c r="M5" s="41">
+        <v>72</v>
+      </c>
+      <c r="N5" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" s="41">
+        <v>11.8</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>13.7</v>
+      </c>
+      <c r="R5" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" s="40">
+        <v>28.1</v>
+      </c>
+      <c r="U5" s="40">
+        <v>40</v>
+      </c>
+      <c r="V5" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="W5" s="41">
+        <v>537</v>
+      </c>
+      <c r="X5" s="42"/>
+    </row>
+    <row r="6" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B6" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="40">
+        <v>2400</v>
+      </c>
+      <c r="D6" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="41">
+        <v>1.2</v>
+      </c>
+      <c r="F6" s="40">
+        <v>69.966999999999999</v>
+      </c>
+      <c r="G6" s="40">
+        <v>55.179000000000002</v>
+      </c>
+      <c r="H6" s="40">
+        <v>95</v>
+      </c>
+      <c r="I6" s="40">
+        <v>80</v>
+      </c>
+      <c r="J6" s="40">
+        <v>67</v>
+      </c>
+      <c r="K6" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="41">
+        <v>62000</v>
+      </c>
+      <c r="O6" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6" s="41">
+        <v>12</v>
+      </c>
+      <c r="Q6" s="41">
+        <v>17.2</v>
+      </c>
+      <c r="R6" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="S6" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="T6" s="40">
+        <v>12.2</v>
+      </c>
+      <c r="U6" s="40">
+        <v>15</v>
+      </c>
+      <c r="V6" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="W6" s="41">
+        <v>708</v>
+      </c>
+      <c r="X6" s="42"/>
+    </row>
+    <row r="7" spans="2:24" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="44">
+        <v>8401</v>
+      </c>
+      <c r="D7" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" s="47">
+        <v>230.2</v>
+      </c>
+      <c r="G7" s="47">
+        <v>177.25399999999999</v>
+      </c>
+      <c r="H7" s="44">
+        <v>95</v>
+      </c>
+      <c r="I7" s="48">
+        <v>80</v>
+      </c>
+      <c r="J7" s="48">
+        <v>67</v>
+      </c>
+      <c r="K7" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" s="49">
+        <v>220000</v>
+      </c>
+      <c r="O7" s="49">
+        <v>122000</v>
+      </c>
+      <c r="P7" s="50">
+        <v>10.6</v>
+      </c>
+      <c r="Q7" s="50">
+        <v>14.35</v>
+      </c>
+      <c r="R7" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="S7" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="T7" s="45">
+        <v>98.7</v>
+      </c>
+      <c r="U7" s="48">
+        <v>125</v>
+      </c>
+      <c r="V7" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="W7" s="44">
+        <v>2354</v>
+      </c>
+      <c r="X7" s="51"/>
+    </row>
+    <row r="8" spans="2:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="X8" s="53"/>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B9" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="X9" s="53"/>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B10" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="X10" s="53"/>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B11" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="X11" s="53"/>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B12" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="X12" s="53"/>
+    </row>
+    <row r="13" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B13" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="X13" s="53"/>
+    </row>
+    <row r="14" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B14" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="X14" s="53"/>
+    </row>
+    <row r="15" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B15" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="X15" s="53"/>
+    </row>
+    <row r="16" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B16" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="X16" s="53"/>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B17" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="X17" s="53"/>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B18" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="X18" s="53"/>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B19" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="X19" s="53"/>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B20" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="X20" s="53"/>
+    </row>
+    <row r="21" spans="2:24" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="54"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="55"/>
+      <c r="P21" s="55"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="55"/>
+      <c r="U21" s="55"/>
+      <c r="V21" s="55"/>
+      <c r="W21" s="55"/>
+      <c r="X21" s="56"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B1:X1"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="X2:X3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C1:Y14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1376,83 +2111,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:25" ht="36.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="75"/>
-      <c r="W1" s="75"/>
-      <c r="X1" s="75"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="77"/>
+      <c r="T1" s="77"/>
+      <c r="U1" s="77"/>
+      <c r="V1" s="77"/>
+      <c r="W1" s="77"/>
+      <c r="X1" s="77"/>
       <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="3:25" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="67" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="70" t="s">
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="73" t="s">
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70"/>
+      <c r="V2" s="70"/>
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="3"/>
     </row>
     <row r="3" spans="3:25" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="76" t="s">
+      <c r="H3" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="73" t="s">
+      <c r="I3" s="70" t="s">
         <v>24</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -1461,60 +2196,60 @@
       <c r="K3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="73" t="s">
+      <c r="L3" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="73" t="s">
+      <c r="M3" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="73" t="s">
+      <c r="N3" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="70" t="s">
+      <c r="O3" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="67" t="s">
+      <c r="P3" s="76"/>
+      <c r="Q3" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="R3" s="69"/>
-      <c r="S3" s="73" t="s">
+      <c r="R3" s="73"/>
+      <c r="S3" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="T3" s="73" t="s">
+      <c r="T3" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="U3" s="73" t="s">
+      <c r="U3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="V3" s="74" t="s">
+      <c r="V3" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="W3" s="73" t="s">
+      <c r="W3" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="X3" s="73" t="s">
+      <c r="X3" s="70" t="s">
         <v>8</v>
       </c>
       <c r="Y3" s="3"/>
     </row>
     <row r="4" spans="3:25" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="73"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="70"/>
       <c r="J4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="70"/>
       <c r="O4" s="6" t="s">
         <v>29</v>
       </c>
@@ -1527,12 +2262,12 @@
       <c r="R4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="74"/>
-      <c r="W4" s="73"/>
-      <c r="X4" s="73"/>
+      <c r="S4" s="70"/>
+      <c r="T4" s="70"/>
+      <c r="U4" s="70"/>
+      <c r="V4" s="79"/>
+      <c r="W4" s="70"/>
+      <c r="X4" s="70"/>
       <c r="Y4" s="3"/>
     </row>
     <row r="5" spans="3:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1841,431 +2576,13 @@
     <mergeCell ref="V3:V4"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
+    <mergeCell ref="U3:U4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="F2:N2"/>
     <mergeCell ref="O2:R2"/>
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="U3:U4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEC4B0F-EED3-4EBA-B5E5-50BB4D88826B}">
-  <dimension ref="C1:W12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="9.33203125" style="22"/>
-    <col min="3" max="3" width="23.33203125" style="22" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" style="22" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="22" customWidth="1"/>
-    <col min="6" max="6" width="15.1640625" style="22" customWidth="1"/>
-    <col min="7" max="8" width="12.6640625" style="22" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" style="22" customWidth="1"/>
-    <col min="10" max="10" width="18.6640625" style="22" customWidth="1"/>
-    <col min="11" max="11" width="8" style="22" customWidth="1"/>
-    <col min="12" max="12" width="20" style="22" customWidth="1"/>
-    <col min="13" max="13" width="6.83203125" style="22" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" style="22" customWidth="1"/>
-    <col min="15" max="15" width="14" style="22" customWidth="1"/>
-    <col min="16" max="16" width="12.6640625" style="22" customWidth="1"/>
-    <col min="17" max="17" width="10.5" style="22" customWidth="1"/>
-    <col min="18" max="18" width="11.5" style="22" customWidth="1"/>
-    <col min="19" max="19" width="28" style="22" customWidth="1"/>
-    <col min="20" max="20" width="23.5" style="22" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.33203125" style="22" customWidth="1"/>
-    <col min="22" max="22" width="38.1640625" style="22" customWidth="1"/>
-    <col min="23" max="23" width="75.83203125" style="22" customWidth="1"/>
-    <col min="24" max="16384" width="9.33203125" style="22"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="3:23" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="63"/>
-      <c r="W1" s="21"/>
-    </row>
-    <row r="2" spans="3:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="55" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="55" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="55" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2" s="60"/>
-      <c r="I2" s="55" t="s">
-        <v>61</v>
-      </c>
-      <c r="J2" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="K2" s="65" t="s">
-        <v>62</v>
-      </c>
-      <c r="L2" s="57" t="s">
-        <v>87</v>
-      </c>
-      <c r="M2" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="N2" s="59"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="55" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q2" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="R2" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="S2" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="T2" s="57" t="s">
-        <v>83</v>
-      </c>
-      <c r="U2" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="V2" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="W2" s="23"/>
-    </row>
-    <row r="3" spans="3:23" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="80"/>
-      <c r="W3" s="23"/>
-    </row>
-    <row r="4" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C4" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="53">
-        <v>35.417999999999999</v>
-      </c>
-      <c r="E4" s="28">
-        <v>27.395</v>
-      </c>
-      <c r="F4" s="30">
-        <v>95</v>
-      </c>
-      <c r="G4" s="30">
-        <v>80</v>
-      </c>
-      <c r="H4" s="30">
-        <v>67</v>
-      </c>
-      <c r="I4" s="29">
-        <v>1265</v>
-      </c>
-      <c r="J4" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="K4" s="32">
-        <v>0.75</v>
-      </c>
-      <c r="L4" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="N4" s="30">
-        <v>45</v>
-      </c>
-      <c r="O4" s="27">
-        <v>36.450000000000003</v>
-      </c>
-      <c r="P4" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q4" s="28">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="R4" s="77">
-        <v>30</v>
-      </c>
-      <c r="S4" s="81" t="s">
-        <v>80</v>
-      </c>
-      <c r="T4" s="81" t="s">
-        <v>84</v>
-      </c>
-      <c r="U4" s="82" t="s">
-        <v>39</v>
-      </c>
-      <c r="V4" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="W4" s="23"/>
-    </row>
-    <row r="5" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C5" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="54">
-        <v>46.220999999999997</v>
-      </c>
-      <c r="E5" s="35">
-        <v>36.290999999999997</v>
-      </c>
-      <c r="F5" s="38">
-        <v>95</v>
-      </c>
-      <c r="G5" s="38">
-        <v>80</v>
-      </c>
-      <c r="H5" s="38">
-        <v>67</v>
-      </c>
-      <c r="I5" s="36">
-        <v>1660</v>
-      </c>
-      <c r="J5" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="K5" s="37">
-        <v>1.2</v>
-      </c>
-      <c r="L5" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" s="38">
-        <v>115</v>
-      </c>
-      <c r="O5" s="34">
-        <v>93.15</v>
-      </c>
-      <c r="P5" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q5" s="35">
-        <v>10.6</v>
-      </c>
-      <c r="R5" s="78">
-        <v>15</v>
-      </c>
-      <c r="S5" s="84" t="s">
-        <v>81</v>
-      </c>
-      <c r="T5" s="81" t="s">
-        <v>85</v>
-      </c>
-      <c r="U5" s="82" t="s">
-        <v>39</v>
-      </c>
-      <c r="V5" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="W5" s="23"/>
-    </row>
-    <row r="6" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C6" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="42"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="31"/>
-    </row>
-    <row r="7" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C7" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="31"/>
-    </row>
-    <row r="8" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C8" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="24"/>
-    </row>
-    <row r="9" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C9" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="V9" s="46"/>
-    </row>
-    <row r="10" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C10" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="V10" s="46"/>
-    </row>
-    <row r="11" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C11" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="V11" s="46"/>
-    </row>
-    <row r="12" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C12" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="47"/>
-      <c r="V12" s="48"/>
-    </row>
-  </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="C1:V1"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
